--- a/data/raw/常见问答.xlsx
+++ b/data/raw/常见问答.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>问题</t>
   </si>
@@ -38,19 +38,52 @@
     <t>灵山胜境在哪里</t>
   </si>
   <si>
-    <t>江苏省无锡市滨湖区马山街道</t>
+    <t>灵山胜境位于江苏省无锡市滨湖区马山街道，地处太湖西北部的马山镇，被秦履峰、青龙山、白虎山三山环抱，占地面积约30万平方米，是国家5A级旅游景区。</t>
   </si>
   <si>
     <t>开放时间</t>
   </si>
   <si>
-    <t>全年 07:30 - 17:30</t>
-  </si>
-  <si>
-    <t>推荐游览路线</t>
-  </si>
-  <si>
-    <t>照壁→佛手广场→梵宫→五印坛城→灵山小镇</t>
+    <t>景区全年开放时间为 07:30 - 17:30。其中灵山梵宫、五印坛城等室内场馆的开放时间一般为 09:00 - 17:00（冬季可能提前至16:30闭馆）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">门票价格及优惠政策是怎样的？
+</t>
+  </si>
+  <si>
+    <t>成人票：210元/人。半价票（105元）：6-18周岁未成年人、全日制本科及以下学生、60-69周岁老人。免票：6周岁以下或1.4米以下儿童、70周岁以上老人、现役军人、残疾人。推荐购买网购联票（225元），包含门票和无限次观光车，更为划算。</t>
+  </si>
+  <si>
+    <t>灵山大佛有多高？是什么材质的？</t>
+  </si>
+  <si>
+    <t>灵山大佛通高88米（佛体79米+莲花瓣9米），含台基总高101.5米。总用铜量达725吨，由2000块铸铜面板拼接焊接而成，是世界最高露天青铜释迦牟尼立像。</t>
+  </si>
+  <si>
+    <t>景区内有哪些不可错过的演出？分别在什么时间？</t>
+  </si>
+  <si>
+    <t>九龙灌浴：再现佛陀诞生“花开见佛”场景。平日演出时间约10:00、11:30、13:30、15:00（周末及节假日加场，每场约15分钟）。
+《灵山吉祥颂》：在灵山梵宫圣坛内上演的大型情景演出。演出时间为10:35、11:30、14:00、16:00（每场约20分钟，凭大门票免费入场，建议提前30分钟排队）。</t>
+  </si>
+  <si>
+    <t>推荐游览路线有哪些</t>
+  </si>
+  <si>
+    <t>推荐经典中轴线深度游路线：
+大照壁 → 五明桥 → 佛足坛 → 五智门 → 菩提大道 → 九龙灌浴 → 降魔浮雕 → 阿育王柱 → 祥符禅寺 → 灵山大佛（登云道、抱佛脚） → 灵山梵宫（看《吉祥颂》） → 五印坛城 → 曼飞龙塔 → 出口。</t>
+  </si>
+  <si>
+    <t>景区内有观光车吗？</t>
+  </si>
+  <si>
+    <t>有的。景区提供观光车服务，单次购票40元/人；若购买225元的门票+观光车联票，则可在当日内无限次乘坐，适合带老人小孩或体力有限的游客。</t>
+  </si>
+  <si>
+    <t>在灵山梵宫参观需要注意什么？</t>
+  </si>
+  <si>
+    <t>灵山梵宫被誉为“东方卢浮宫”，内部有大量非遗艺术瑰宝（如琉璃壁画、星空穹顶、东阳木雕）。参观时请注意保持安静，禁止触摸文物展柜与佛像；拍照时禁止使用闪光灯，以免损伤油画与琉璃作品；部分区域（如圣坛）演出时需按指定位置就坐，不可随意走动。</t>
   </si>
 </sst>
 </file>
@@ -664,8 +697,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1012,8 +1048,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1039,12 +1075,52 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="4" ht="67.5" spans="1:2">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="391.5" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
